--- a/Análisis programas postgrado SNIES/Modificados posgrado.xlsx
+++ b/Análisis programas postgrado SNIES/Modificados posgrado.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -16,22 +16,17 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -42,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -50,23 +45,13 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -436,222 +421,222 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>CÓDIGO_INSTITUCIÓN</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>NOMBRE_INSTITUCIÓN</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>SECTOR</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>DEPARTAMENTO_OFERTA_PROGRAMA</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>MUNICIPIO_OFERTA_PROGRAMA</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>CÓDIGO_SNIES_DEL_PROGRAMA</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>NOMBRE_DEL_PROGRAMA</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>MODALIDAD</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>NÚMERO_CRÉDITOS</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>NÚMERO_PERIODOS_DE_DURACIÓN</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>PERIODICIDAD</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>COSTO_MATRÍCULA_ESTUD_NUEVOS</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>PERIODICIDAD_ADMISIONES</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>FECHA_DE_REGISTRO_EN_SNIES</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>CINE_F_2013_AC_CAMPO_AMPLIO</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>CINE_F_2013_AC_CAMPO_ESPECÍFIC</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>CINE_F_2013_AC_CAMPO_DETALLADO</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>NÚCLEO_BÁSICO_DEL_CONOCIMIENTO</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>NIVEL_DE_FORMACIÓN</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>PROGINSTI</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>NÚMERO_CRÉDITOS_NUEVOS</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>NÚMERO_CRÉDITOS_ANTERIORES</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>FECHA_OBTENCION</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>DIVISIÓN UNINORTE</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>Estado</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>CÓDIGO_INSTITUCIÓN_ANTERIOR</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>NOMBRE_INSTITUCIÓN_ANTERIOR</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>SECTOR_ANTERIOR</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>DEPARTAMENTO_OFERTA_PROGRAMA_ANTERIOR</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>MUNICIPIO_OFERTA_PROGRAMA_ANTERIOR</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>NOMBRE_DEL_PROGRAMA_ANTERIOR</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>MODALIDAD_ANTERIOR</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>NÚMERO_CRÉDITOS_ANTERIOR</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>NÚMERO_PERIODOS_DE_DURACIÓN_ANTERIOR</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>PERIODICIDAD_ANTERIOR</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>COSTO_MATRÍCULA_ESTUD_NUEVOS_ANTERIOR</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>PERIODICIDAD_ADMISIONES_ANTERIOR</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>FECHA_DE_REGISTRO_EN_SNIES_ANTERIOR</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>CINE_F_2013_AC_CAMPO_AMPLIO_ANTERIOR</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>CINE_F_2013_AC_CAMPO_ESPECÍFIC_ANTERIOR</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>CINE_F_2013_AC_CAMPO_DETALLADO_ANTERIOR</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AP1" t="inlineStr">
         <is>
           <t>NÚCLEO_BÁSICO_DEL_CONOCIMIENTO_ANTERIOR</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AQ1" t="inlineStr">
         <is>
           <t>NIVEL_DE_FORMACIÓN_ANTERIOR</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AR1" t="inlineStr">
         <is>
           <t>QUE_CAMBIO</t>
         </is>
@@ -713,7 +698,7 @@
           <t>Por cohorte</t>
         </is>
       </c>
-      <c r="N2" s="2" t="n">
+      <c r="N2" s="1" t="n">
         <v>44572</v>
       </c>
       <c r="O2" t="inlineStr">
@@ -843,7 +828,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N3" s="2" t="n">
+      <c r="N3" s="1" t="n">
         <v>44755</v>
       </c>
       <c r="O3" t="inlineStr">
@@ -973,7 +958,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N4" s="2" t="n">
+      <c r="N4" s="1" t="n">
         <v>44299</v>
       </c>
       <c r="O4" t="inlineStr">
@@ -1103,7 +1088,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N5" s="2" t="n">
+      <c r="N5" s="1" t="n">
         <v>44295</v>
       </c>
       <c r="O5" t="inlineStr">
@@ -1233,7 +1218,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N6" s="2" t="n">
+      <c r="N6" s="1" t="n">
         <v>44725</v>
       </c>
       <c r="O6" t="inlineStr">
@@ -1363,7 +1348,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N7" s="2" t="n">
+      <c r="N7" s="1" t="n">
         <v>44671</v>
       </c>
       <c r="O7" t="inlineStr">
@@ -1493,7 +1478,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N8" s="2" t="n">
+      <c r="N8" s="1" t="n">
         <v>44299</v>
       </c>
       <c r="O8" t="inlineStr">
@@ -1623,7 +1608,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N9" s="2" t="n">
+      <c r="N9" s="1" t="n">
         <v>44292</v>
       </c>
       <c r="O9" t="inlineStr">
@@ -1698,10 +1683,8 @@
       <c r="AR9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>1101</t>
-        </is>
+      <c r="A10" t="n">
+        <v>1101</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -1751,7 +1734,7 @@
         <v>11413000</v>
       </c>
       <c r="M10" t="inlineStr"/>
-      <c r="N10" s="3" t="n">
+      <c r="N10" s="1" t="n">
         <v>40156</v>
       </c>
       <c r="O10" t="inlineStr">
@@ -1797,10 +1780,8 @@
           <t>Activo</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>1101</t>
-        </is>
+      <c r="Z10" t="n">
+        <v>1101</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
@@ -1851,7 +1832,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="AL10" s="3" t="n">
+      <c r="AL10" s="1" t="n">
         <v>41844</v>
       </c>
       <c r="AM10" t="inlineStr">
@@ -1886,10 +1867,8 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>1102</t>
-        </is>
+      <c r="A11" t="n">
+        <v>1102</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -1939,7 +1918,7 @@
         <v>9515000</v>
       </c>
       <c r="M11" t="inlineStr"/>
-      <c r="N11" s="3" t="n">
+      <c r="N11" s="1" t="n">
         <v>39195</v>
       </c>
       <c r="O11" t="inlineStr">
@@ -1985,10 +1964,8 @@
           <t>Activo</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>1102</t>
-        </is>
+      <c r="Z11" t="n">
+        <v>1102</v>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
@@ -2039,7 +2016,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="AL11" s="3" t="n">
+      <c r="AL11" s="1" t="n">
         <v>45390</v>
       </c>
       <c r="AM11" t="inlineStr">
@@ -2074,10 +2051,8 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>1102</t>
-        </is>
+      <c r="A12" t="n">
+        <v>1102</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -2131,7 +2106,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N12" s="3" t="n">
+      <c r="N12" s="1" t="n">
         <v>41094</v>
       </c>
       <c r="O12" t="inlineStr">
@@ -2177,10 +2152,8 @@
           <t>Activo</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>1102</t>
-        </is>
+      <c r="Z12" t="n">
+        <v>1102</v>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
@@ -2231,7 +2204,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="AL12" s="3" t="n">
+      <c r="AL12" s="1" t="n">
         <v>41094</v>
       </c>
       <c r="AM12" t="inlineStr">
@@ -2266,10 +2239,8 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>1203</t>
-        </is>
+      <c r="A13" t="n">
+        <v>1203</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -2323,7 +2294,7 @@
           <t>Por cohorte</t>
         </is>
       </c>
-      <c r="N13" s="3" t="n">
+      <c r="N13" s="1" t="n">
         <v>35875</v>
       </c>
       <c r="O13" t="inlineStr">
@@ -2369,10 +2340,8 @@
           <t>Activo</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>1203</t>
-        </is>
+      <c r="Z13" t="n">
+        <v>1203</v>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
@@ -2423,7 +2392,7 @@
           <t>Por cohorte</t>
         </is>
       </c>
-      <c r="AL13" s="3" t="n">
+      <c r="AL13" s="1" t="n">
         <v>44348</v>
       </c>
       <c r="AM13" t="inlineStr">
@@ -2458,10 +2427,8 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>1204</t>
-        </is>
+      <c r="A14" t="n">
+        <v>1204</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -2515,7 +2482,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N14" s="3" t="n">
+      <c r="N14" s="1" t="n">
         <v>39490</v>
       </c>
       <c r="O14" t="inlineStr">
@@ -2561,10 +2528,8 @@
           <t>Activo</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>1204</t>
-        </is>
+      <c r="Z14" t="n">
+        <v>1204</v>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
@@ -2615,7 +2580,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="AL14" s="3" t="n">
+      <c r="AL14" s="1" t="n">
         <v>45037</v>
       </c>
       <c r="AM14" t="inlineStr">
@@ -2650,10 +2615,8 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>1221</t>
-        </is>
+      <c r="A15" t="n">
+        <v>1221</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -2707,7 +2670,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N15" s="3" t="n">
+      <c r="N15" s="1" t="n">
         <v>39118</v>
       </c>
       <c r="O15" t="inlineStr">
@@ -2753,10 +2716,8 @@
           <t>Activo</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>1201</t>
-        </is>
+      <c r="Z15" t="n">
+        <v>1201</v>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
@@ -2805,7 +2766,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="AL15" s="3" t="n">
+      <c r="AL15" s="1" t="n">
         <v>44377</v>
       </c>
       <c r="AM15" t="inlineStr">
@@ -2840,10 +2801,8 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>1221</t>
-        </is>
+      <c r="A16" t="n">
+        <v>1221</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -2897,7 +2856,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N16" s="3" t="n">
+      <c r="N16" s="1" t="n">
         <v>38919</v>
       </c>
       <c r="O16" t="inlineStr">
@@ -2943,10 +2902,8 @@
           <t>Activo</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>1201</t>
-        </is>
+      <c r="Z16" t="n">
+        <v>1201</v>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
@@ -2995,7 +2952,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="AL16" s="3" t="n">
+      <c r="AL16" s="1" t="n">
         <v>44448</v>
       </c>
       <c r="AM16" t="inlineStr">
@@ -3030,10 +2987,8 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>1704</t>
-        </is>
+      <c r="A17" t="n">
+        <v>1704</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -3087,7 +3042,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N17" s="3" t="n">
+      <c r="N17" s="1" t="n">
         <v>44532</v>
       </c>
       <c r="O17" t="inlineStr">
@@ -3133,10 +3088,8 @@
           <t>Activo</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>1704</t>
-        </is>
+      <c r="Z17" t="n">
+        <v>1704</v>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
@@ -3187,7 +3140,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="AL17" s="3" t="n">
+      <c r="AL17" s="1" t="n">
         <v>44340</v>
       </c>
       <c r="AM17" t="inlineStr">
@@ -3222,10 +3175,8 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>1714</t>
-        </is>
+      <c r="A18" t="n">
+        <v>1714</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -3279,7 +3230,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N18" s="3" t="n">
+      <c r="N18" s="1" t="n">
         <v>44714</v>
       </c>
       <c r="O18" t="inlineStr">
@@ -3325,10 +3276,8 @@
           <t>Activo</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>1714</t>
-        </is>
+      <c r="Z18" t="n">
+        <v>1714</v>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
@@ -3379,7 +3328,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="AL18" s="3" t="n">
+      <c r="AL18" s="1" t="n">
         <v>44692</v>
       </c>
       <c r="AM18" t="inlineStr">
@@ -3414,10 +3363,8 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>1714</t>
-        </is>
+      <c r="A19" t="n">
+        <v>1714</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -3471,7 +3418,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N19" s="3" t="n">
+      <c r="N19" s="1" t="n">
         <v>44691</v>
       </c>
       <c r="O19" t="inlineStr">
@@ -3517,10 +3464,8 @@
           <t>Activo</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>1714</t>
-        </is>
+      <c r="Z19" t="n">
+        <v>1714</v>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
@@ -3571,7 +3516,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="AL19" s="3" t="n">
+      <c r="AL19" s="1" t="n">
         <v>43529</v>
       </c>
       <c r="AM19" t="inlineStr">
@@ -3606,10 +3551,8 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>1714</t>
-        </is>
+      <c r="A20" t="n">
+        <v>1714</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -3661,7 +3604,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N20" s="3" t="n">
+      <c r="N20" s="1" t="n">
         <v>41309</v>
       </c>
       <c r="O20" t="inlineStr">
@@ -3707,10 +3650,8 @@
           <t>Activo</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>1714</t>
-        </is>
+      <c r="Z20" t="n">
+        <v>1714</v>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
@@ -3759,7 +3700,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="AL20" s="3" t="n">
+      <c r="AL20" s="1" t="n">
         <v>41324</v>
       </c>
       <c r="AM20" t="inlineStr">
@@ -3794,10 +3735,8 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>1734</t>
-        </is>
+      <c r="A21" t="n">
+        <v>1734</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -3849,7 +3788,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N21" s="3" t="n">
+      <c r="N21" s="1" t="n">
         <v>45649</v>
       </c>
       <c r="O21" t="inlineStr">
@@ -3895,10 +3834,8 @@
           <t>Activo</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>1734</t>
-        </is>
+      <c r="Z21" t="n">
+        <v>1734</v>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
@@ -3947,7 +3884,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="AL21" s="3" t="n">
+      <c r="AL21" s="1" t="n">
         <v>45649</v>
       </c>
       <c r="AM21" t="inlineStr">
@@ -3982,10 +3919,8 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>1801</t>
-        </is>
+      <c r="A22" t="n">
+        <v>1801</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -4039,7 +3974,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N22" s="3" t="n">
+      <c r="N22" s="1" t="n">
         <v>40605</v>
       </c>
       <c r="O22" t="inlineStr">
@@ -4085,10 +4020,8 @@
           <t>Activo</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>1801</t>
-        </is>
+      <c r="Z22" t="n">
+        <v>1801</v>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
@@ -4139,7 +4072,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="AL22" s="3" t="n">
+      <c r="AL22" s="1" t="n">
         <v>43153</v>
       </c>
       <c r="AM22" t="inlineStr">
@@ -4174,10 +4107,8 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>1803</t>
-        </is>
+      <c r="A23" t="n">
+        <v>1803</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -4231,7 +4162,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N23" s="3" t="n">
+      <c r="N23" s="1" t="n">
         <v>39107</v>
       </c>
       <c r="O23" t="inlineStr">
@@ -4277,10 +4208,8 @@
           <t>Activo</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>1803</t>
-        </is>
+      <c r="Z23" t="n">
+        <v>1803</v>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
@@ -4331,7 +4260,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="AL23" s="3" t="n">
+      <c r="AL23" s="1" t="n">
         <v>44126</v>
       </c>
       <c r="AM23" t="inlineStr">
@@ -4366,10 +4295,8 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>1812</t>
-        </is>
+      <c r="A24" t="n">
+        <v>1812</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -4421,7 +4348,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N24" s="3" t="n">
+      <c r="N24" s="1" t="n">
         <v>40372</v>
       </c>
       <c r="O24" t="inlineStr">
@@ -4467,10 +4394,8 @@
           <t>Activo</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>1812</t>
-        </is>
+      <c r="Z24" t="n">
+        <v>1812</v>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
@@ -4519,7 +4444,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="AL24" s="3" t="n">
+      <c r="AL24" s="1" t="n">
         <v>42909</v>
       </c>
       <c r="AM24" t="inlineStr">
@@ -4554,10 +4479,8 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>1815</t>
-        </is>
+      <c r="A25" t="n">
+        <v>1815</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -4611,7 +4534,7 @@
           <t>Trimestral</t>
         </is>
       </c>
-      <c r="N25" s="3" t="n">
+      <c r="N25" s="1" t="n">
         <v>35875</v>
       </c>
       <c r="O25" t="inlineStr">
@@ -4657,10 +4580,8 @@
           <t>Activo</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>1815</t>
-        </is>
+      <c r="Z25" t="n">
+        <v>1815</v>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
@@ -4711,7 +4632,7 @@
           <t>Trimestral</t>
         </is>
       </c>
-      <c r="AL25" s="3" t="n">
+      <c r="AL25" s="1" t="n">
         <v>43817</v>
       </c>
       <c r="AM25" t="inlineStr">
@@ -4746,10 +4667,8 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>1825</t>
-        </is>
+      <c r="A26" t="n">
+        <v>1825</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -4803,7 +4722,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N26" s="3" t="n">
+      <c r="N26" s="1" t="n">
         <v>42211</v>
       </c>
       <c r="O26" t="inlineStr">
@@ -4849,10 +4768,8 @@
           <t>Activo</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>1825</t>
-        </is>
+      <c r="Z26" t="n">
+        <v>1825</v>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
@@ -4903,7 +4820,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="AL26" s="3" t="n">
+      <c r="AL26" s="1" t="n">
         <v>44453</v>
       </c>
       <c r="AM26" t="inlineStr">
@@ -4938,10 +4855,8 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>1830</t>
-        </is>
+      <c r="A27" t="n">
+        <v>1830</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -4993,7 +4908,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N27" s="3" t="n">
+      <c r="N27" s="1" t="n">
         <v>44161</v>
       </c>
       <c r="O27" t="inlineStr">
@@ -5039,10 +4954,8 @@
           <t>Activo</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>1830</t>
-        </is>
+      <c r="Z27" t="n">
+        <v>1830</v>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
@@ -5091,7 +5004,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="AL27" s="3" t="n">
+      <c r="AL27" s="1" t="n">
         <v>44146</v>
       </c>
       <c r="AM27" t="inlineStr">
@@ -5126,10 +5039,8 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>2106</t>
-        </is>
+      <c r="A28" t="n">
+        <v>2106</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -5183,7 +5094,7 @@
           <t>Por cohorte</t>
         </is>
       </c>
-      <c r="N28" s="3" t="n">
+      <c r="N28" s="1" t="n">
         <v>40121</v>
       </c>
       <c r="O28" t="inlineStr">
@@ -5229,10 +5140,8 @@
           <t>Activo</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>2106</t>
-        </is>
+      <c r="Z28" t="n">
+        <v>2106</v>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
@@ -5283,7 +5192,7 @@
           <t>Por cohorte</t>
         </is>
       </c>
-      <c r="AL28" s="3" t="n">
+      <c r="AL28" s="1" t="n">
         <v>43053</v>
       </c>
       <c r="AM28" t="inlineStr">
@@ -5318,10 +5227,8 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>2708</t>
-        </is>
+      <c r="A29" t="n">
+        <v>2708</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -5375,7 +5282,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N29" s="3" t="n">
+      <c r="N29" s="1" t="n">
         <v>35875</v>
       </c>
       <c r="O29" t="inlineStr">
@@ -5421,10 +5328,8 @@
           <t>Activo</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>2708</t>
-        </is>
+      <c r="Z29" t="n">
+        <v>2708</v>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
@@ -5475,7 +5380,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="AL29" s="3" t="n">
+      <c r="AL29" s="1" t="n">
         <v>44189</v>
       </c>
       <c r="AM29" t="inlineStr">
@@ -5510,10 +5415,8 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>2708</t>
-        </is>
+      <c r="A30" t="n">
+        <v>2708</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -5567,7 +5470,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N30" s="3" t="n">
+      <c r="N30" s="1" t="n">
         <v>36280</v>
       </c>
       <c r="O30" t="inlineStr">
@@ -5613,10 +5516,8 @@
           <t>Activo</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>2708</t>
-        </is>
+      <c r="Z30" t="n">
+        <v>2708</v>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
@@ -5667,7 +5568,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="AL30" s="3" t="n">
+      <c r="AL30" s="1" t="n">
         <v>44189</v>
       </c>
       <c r="AM30" t="inlineStr">
@@ -5702,10 +5603,8 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>2719</t>
-        </is>
+      <c r="A31" t="n">
+        <v>2719</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
@@ -5759,7 +5658,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N31" s="3" t="n">
+      <c r="N31" s="1" t="n">
         <v>40135</v>
       </c>
       <c r="O31" t="inlineStr">
@@ -5805,10 +5704,8 @@
           <t>Activo</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>2719</t>
-        </is>
+      <c r="Z31" t="n">
+        <v>2719</v>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
@@ -5859,7 +5756,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="AL31" s="3" t="n">
+      <c r="AL31" s="1" t="n">
         <v>44572</v>
       </c>
       <c r="AM31" t="inlineStr">
@@ -5894,10 +5791,8 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>2719</t>
-        </is>
+      <c r="A32" t="n">
+        <v>2719</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
@@ -5951,7 +5846,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N32" s="3" t="n">
+      <c r="N32" s="1" t="n">
         <v>40980</v>
       </c>
       <c r="O32" t="inlineStr">
@@ -5997,10 +5892,8 @@
           <t>Activo</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>2719</t>
-        </is>
+      <c r="Z32" t="n">
+        <v>2719</v>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
@@ -6051,7 +5944,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="AL32" s="3" t="n">
+      <c r="AL32" s="1" t="n">
         <v>43312</v>
       </c>
       <c r="AM32" t="inlineStr">
@@ -6086,10 +5979,8 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>2744</t>
-        </is>
+      <c r="A33" t="n">
+        <v>2744</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
@@ -6143,7 +6034,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N33" s="3" t="n">
+      <c r="N33" s="1" t="n">
         <v>45855</v>
       </c>
       <c r="O33" t="inlineStr">
@@ -6189,10 +6080,8 @@
           <t>Activo</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>2744</t>
-        </is>
+      <c r="Z33" t="n">
+        <v>2744</v>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
@@ -6241,7 +6130,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="AL33" s="3" t="n">
+      <c r="AL33" s="1" t="n">
         <v>45855</v>
       </c>
       <c r="AM33" t="inlineStr">
@@ -6276,10 +6165,8 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>9105</t>
-        </is>
+      <c r="A34" t="n">
+        <v>9105</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
@@ -6333,7 +6220,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N34" s="3" t="n">
+      <c r="N34" s="1" t="n">
         <v>38469</v>
       </c>
       <c r="O34" t="inlineStr">
@@ -6379,10 +6266,8 @@
           <t>Activo</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>9105</t>
-        </is>
+      <c r="Z34" t="n">
+        <v>9105</v>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
@@ -6433,7 +6318,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="AL34" s="3" t="n">
+      <c r="AL34" s="1" t="n">
         <v>43161</v>
       </c>
       <c r="AM34" t="inlineStr">
@@ -6468,10 +6353,8 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>9910</t>
-        </is>
+      <c r="A35" t="n">
+        <v>9910</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
@@ -6525,7 +6408,7 @@
           <t>Trimestral</t>
         </is>
       </c>
-      <c r="N35" s="3" t="n">
+      <c r="N35" s="1" t="n">
         <v>44153</v>
       </c>
       <c r="O35" t="inlineStr">
@@ -6571,10 +6454,8 @@
           <t>Activo</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>9910</t>
-        </is>
+      <c r="Z35" t="n">
+        <v>9910</v>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
@@ -6625,7 +6506,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="AL35" s="3" t="n">
+      <c r="AL35" s="1" t="n">
         <v>44153</v>
       </c>
       <c r="AM35" t="inlineStr">
